--- a/data/TablaMorbilidad_Subsectores.xlsx
+++ b/data/TablaMorbilidad_Subsectores.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Downloads\TABLERO_STREAMLIT_DASHBOARD\DASHBOARD_Morbilidad_DESPLIEGUE_2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fernando\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39DA9BA-4CCA-4E7A-9645-E8E995B7930B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8995AB-E40E-42D4-B9F8-0F084D99FEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{3F5E094F-8F70-430D-B0BA-DB553EE45739}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3F5E094F-8F70-430D-B0BA-DB553EE45739}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$D$50</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="21">
   <si>
     <t>labels</t>
   </si>
@@ -55,12 +55,6 @@
   </si>
   <si>
     <t>Meta</t>
-  </si>
-  <si>
-    <t>Accid. Transp</t>
-  </si>
-  <si>
-    <t>Agres.</t>
   </si>
   <si>
     <t>Esquizofrenia</t>
@@ -570,14 +564,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{257B41CB-BC06-4035-86EB-862B7C7904CF}">
-  <dimension ref="A1:E58"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -588,13 +582,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
@@ -605,7 +599,7 @@
       <c r="D2" s="12"/>
       <c r="E2" s="12"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
@@ -618,7 +612,7 @@
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
@@ -631,7 +625,7 @@
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
@@ -644,7 +638,7 @@
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>8</v>
       </c>
@@ -657,58 +651,58 @@
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="2">
-        <v>4949.7638369999931</v>
+        <v>14562.013561000027</v>
       </c>
       <c r="D7">
-        <v>1250.0676999999962</v>
+        <v>2260.9653999999937</v>
       </c>
       <c r="E7">
-        <v>39.6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>64.41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="2">
-        <v>1728.0165849999983</v>
+        <v>19704.138970000004</v>
       </c>
       <c r="D8">
-        <v>735.60400000000232</v>
+        <v>2662.7846999999761</v>
       </c>
       <c r="E8">
-        <v>23.49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="2">
-        <v>14562.013561000027</v>
+        <v>2165.8089160000018</v>
       </c>
       <c r="D9">
-        <v>2260.9653999999937</v>
+        <v>902.97770000000105</v>
       </c>
       <c r="E9">
-        <v>64.41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -716,67 +710,67 @@
         <v>5</v>
       </c>
       <c r="C10" s="2">
-        <v>19704.138970000004</v>
+        <v>11340.072553999958</v>
       </c>
       <c r="D10">
-        <v>2662.7846999999761</v>
+        <v>2901.2899999999909</v>
       </c>
       <c r="E10">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+        <v>39.090000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="2">
-        <v>2165.8089160000018</v>
+        <v>10757.731560999993</v>
       </c>
       <c r="D11">
-        <v>902.97770000000105</v>
+        <v>2704.3394999999923</v>
       </c>
       <c r="E11">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+        <v>39.78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="2">
-        <v>11340.072553999958</v>
+        <v>56399.830181000114</v>
       </c>
       <c r="D12">
-        <v>2901.2899999999909</v>
+        <v>4655.2753999999968</v>
       </c>
       <c r="E12">
-        <v>39.090000000000003</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+        <v>121.15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="2">
-        <v>10757.731560999993</v>
+        <v>5682.1123519999965</v>
       </c>
       <c r="D13">
-        <v>2704.3394999999923</v>
+        <v>1699.9487999999963</v>
       </c>
       <c r="E13">
-        <v>39.78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+        <v>33.43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -784,16 +778,16 @@
         <v>5</v>
       </c>
       <c r="C14" s="2">
-        <v>56399.830181000114</v>
+        <v>46452.04955500002</v>
       </c>
       <c r="D14">
-        <v>4655.2753999999968</v>
+        <v>3917.0709000000252</v>
       </c>
       <c r="E14">
-        <v>121.15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+        <v>118.59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -801,16 +795,16 @@
         <v>5</v>
       </c>
       <c r="C15" s="2">
-        <v>5682.1123519999965</v>
+        <v>37392.073117999957</v>
       </c>
       <c r="D15">
-        <v>1699.9487999999963</v>
+        <v>4828.147199999963</v>
       </c>
       <c r="E15">
-        <v>33.43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+        <v>77.45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -818,731 +812,595 @@
         <v>5</v>
       </c>
       <c r="C16" s="2">
-        <v>46452.04955500002</v>
+        <v>15545.761623000053</v>
       </c>
       <c r="D16">
-        <v>3917.0709000000252</v>
+        <v>2864.3186000000069</v>
       </c>
       <c r="E16">
-        <v>118.59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+        <v>54.27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="2">
-        <v>37392.073117999957</v>
+        <v>83705.954608999804</v>
       </c>
       <c r="D17">
-        <v>4828.147199999963</v>
+        <v>5098.2465999999858</v>
       </c>
       <c r="E17">
-        <v>77.45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+        <v>164.19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" s="2">
-        <v>15545.761623000053</v>
+        <v>9066.0146040000145</v>
       </c>
       <c r="D18">
-        <v>2864.3186000000069</v>
+        <v>3189.3510999999967</v>
       </c>
       <c r="E18">
-        <v>54.27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+        <v>28.43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C19" s="2">
-        <v>83705.954608999804</v>
+        <v>17933.946848999909</v>
       </c>
       <c r="D19">
-        <v>5098.2465999999858</v>
+        <v>3651.3966999999907</v>
       </c>
       <c r="E19">
-        <v>164.19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+        <v>49.12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="2">
-        <v>15876.147538000057</v>
+        <v>1331.9157380000013</v>
       </c>
       <c r="D20">
-        <v>3631.7988999999902</v>
+        <v>649.83770000000015</v>
       </c>
       <c r="E20">
-        <v>43.71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="2">
-        <v>3935.4379469999985</v>
+        <v>17615.99904100005</v>
       </c>
       <c r="D21">
-        <v>1827.2416999999959</v>
+        <v>4518.6741999999986</v>
       </c>
       <c r="E21">
-        <v>21.54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+        <v>38.979999999999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="2">
-        <v>9066.0146040000145</v>
+        <v>10884.031548000004</v>
       </c>
       <c r="D22">
-        <v>3189.3510999999967</v>
+        <v>3553.5849999999946</v>
       </c>
       <c r="E22">
-        <v>28.43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+        <v>30.63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="2">
-        <v>17933.946848999909</v>
+        <v>83562.204810999741</v>
       </c>
       <c r="D23">
-        <v>3651.3966999999907</v>
+        <v>6374.6397999999508</v>
       </c>
       <c r="E23">
-        <v>49.12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+        <v>131.09</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C24" s="2">
-        <v>1331.9157380000013</v>
+        <v>4037.9383209999974</v>
       </c>
       <c r="D24">
-        <v>649.83770000000015</v>
+        <v>2146.8174999999987</v>
       </c>
       <c r="E24">
-        <v>20.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+        <v>18.809999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C25" s="2">
-        <v>17615.99904100005</v>
+        <v>60720.360230000137</v>
       </c>
       <c r="D25">
-        <v>4518.6741999999986</v>
+        <v>6117.343899999998</v>
       </c>
       <c r="E25">
-        <v>38.979999999999997</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+        <v>99.26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C26" s="2">
-        <v>10884.031548000004</v>
+        <v>43038.375925999913</v>
       </c>
       <c r="D26">
-        <v>3553.5849999999946</v>
+        <v>7380.0190999999631</v>
       </c>
       <c r="E26">
-        <v>30.63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+        <v>58.32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="2">
-        <v>83562.204810999741</v>
+        <v>15528.48821800005</v>
       </c>
       <c r="D27">
-        <v>6374.6397999999508</v>
+        <v>4007.4281999999771</v>
       </c>
       <c r="E27">
-        <v>131.09</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+        <v>38.75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="2">
-        <v>4037.9383209999974</v>
+        <v>102468.58146399983</v>
       </c>
       <c r="D28">
-        <v>2146.8174999999987</v>
+        <v>7850.3179999999675</v>
       </c>
       <c r="E28">
-        <v>18.809999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+        <v>130.53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C29" s="2">
-        <v>60720.360230000137</v>
+        <v>53432.87993800066</v>
       </c>
       <c r="D29">
-        <v>6117.343899999998</v>
+        <v>18185.669599999979</v>
       </c>
       <c r="E29">
-        <v>99.26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+        <v>29.38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C30" s="2">
-        <v>43038.375925999913</v>
+        <v>89356.371045000516</v>
       </c>
       <c r="D30">
-        <v>7380.0190999999631</v>
+        <v>19261.161199999857</v>
       </c>
       <c r="E30">
-        <v>58.32</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+        <v>46.39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2">
+        <v>4726.3945179999919</v>
+      </c>
+      <c r="D31">
+        <v>7361.3686999999663</v>
+      </c>
+      <c r="E31">
+        <v>6.42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="2">
+        <v>72902.407781000118</v>
+      </c>
+      <c r="D32">
+        <v>25127.897699999445</v>
+      </c>
+      <c r="E32">
+        <v>29.01</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>18</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="2">
-        <v>15528.48821800005</v>
-      </c>
-      <c r="D31">
-        <v>4007.4281999999771</v>
-      </c>
-      <c r="E31">
-        <v>38.75</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>19</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="2">
-        <v>102468.58146399983</v>
-      </c>
-      <c r="D32">
-        <v>7850.3179999999675</v>
-      </c>
-      <c r="E32">
-        <v>130.53</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>9</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="2">
-        <v>26913.164510999708</v>
+        <v>40615.253829000314</v>
       </c>
       <c r="D33">
-        <v>14128.525100000041</v>
+        <v>20383.673699999908</v>
       </c>
       <c r="E33">
-        <v>19.05</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+        <v>19.93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="2">
-        <v>8294.7356719999625</v>
+        <v>223155.02447799902</v>
       </c>
       <c r="D34">
-        <v>12999.45489999995</v>
+        <v>26748.365799999512</v>
       </c>
       <c r="E34">
-        <v>6.38</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+        <v>83.43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="2">
-        <v>53432.87993800066</v>
+        <v>19710.470080999879</v>
       </c>
       <c r="D35">
-        <v>18185.669599999979</v>
+        <v>17064.418199999989</v>
       </c>
       <c r="E35">
-        <v>29.38</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+        <v>11.55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="2">
-        <v>89356.371045000516</v>
+        <v>154268.26948799912</v>
       </c>
       <c r="D36">
-        <v>19261.161199999857</v>
+        <v>28610.576299999753</v>
       </c>
       <c r="E36">
-        <v>46.39</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+        <v>53.92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="2">
-        <v>4726.3945179999919</v>
+        <v>103423.89928300043</v>
       </c>
       <c r="D37">
-        <v>7361.3686999999663</v>
+        <v>31342.653199999288</v>
       </c>
       <c r="E37">
-        <v>6.42</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="2">
-        <v>72902.407781000118</v>
+        <v>79959.711067001073</v>
       </c>
       <c r="D38">
-        <v>25127.897699999445</v>
+        <v>20904.569099999891</v>
       </c>
       <c r="E38">
-        <v>29.01</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+        <v>38.25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>20</v>
-      </c>
-      <c r="B39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="2">
-        <v>40615.253829000314</v>
+        <v>351299.60072899441</v>
       </c>
       <c r="D39">
-        <v>20383.673699999908</v>
+        <v>35892.676399999385</v>
       </c>
       <c r="E39">
-        <v>19.93</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+        <v>97.88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C40" s="2">
-        <v>223155.02447799902</v>
+        <v>1038.0106050000006</v>
       </c>
       <c r="D40">
-        <v>26748.365799999512</v>
+        <v>191.92730000000006</v>
       </c>
       <c r="E40">
-        <v>83.43</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+        <v>54.08</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C41" s="2">
-        <v>19710.470080999879</v>
+        <v>2106.030721000001</v>
       </c>
       <c r="D41">
-        <v>17064.418199999989</v>
+        <v>250.73500000000024</v>
       </c>
       <c r="E41">
-        <v>11.55</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+        <v>83.99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C42" s="2">
-        <v>154268.26948799912</v>
+        <v>119.99687700000003</v>
       </c>
       <c r="D42">
-        <v>28610.576299999753</v>
+        <v>21.597899999999996</v>
       </c>
       <c r="E42">
-        <v>53.92</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+        <v>55.56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C43" s="2">
-        <v>103423.89928300043</v>
+        <v>1392.0101880000016</v>
       </c>
       <c r="D43">
-        <v>31342.653199999288</v>
+        <v>310.02700000000038</v>
       </c>
       <c r="E43">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>18</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C44" s="2">
-        <v>79959.711067001073</v>
+        <v>1188.0089909999988</v>
       </c>
       <c r="D44">
-        <v>20904.569099999891</v>
+        <v>206.53430000000034</v>
       </c>
       <c r="E44">
-        <v>38.25</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+        <v>57.52</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>19</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="C45" s="2">
-        <v>351299.60072899441</v>
+        <v>4764.0377489999946</v>
       </c>
       <c r="D45">
-        <v>35892.676399999385</v>
+        <v>526.02520000000095</v>
       </c>
       <c r="E45">
-        <v>97.88</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+        <v>90.57</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2">
-        <v>270.00384099999997</v>
+        <v>971.95499300000051</v>
       </c>
       <c r="D46">
-        <v>63.11810000000002</v>
+        <v>145.49510000000009</v>
       </c>
       <c r="E46">
-        <v>42.78</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+        <v>66.8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="2">
-        <v>113.98712299999998</v>
+        <v>1727.9443350000038</v>
       </c>
       <c r="D47">
-        <v>46.441199999999988</v>
+        <v>374.46700000000044</v>
       </c>
       <c r="E47">
-        <v>24.54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+        <v>46.14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="2">
-        <v>1038.0106050000006</v>
+        <v>2801.9819490000018</v>
       </c>
       <c r="D48">
-        <v>191.92730000000006</v>
+        <v>427.40630000000021</v>
       </c>
       <c r="E48">
-        <v>54.08</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+        <v>65.56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="2">
-        <v>2106.030721000001</v>
+        <v>869.96048499999927</v>
       </c>
       <c r="D49">
-        <v>250.73500000000024</v>
+        <v>218.12870000000026</v>
       </c>
       <c r="E49">
-        <v>83.99</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+        <v>39.880000000000003</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>12</v>
-      </c>
-      <c r="B50" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="2">
-        <v>119.99687700000003</v>
+        <v>10386.047237999997</v>
       </c>
       <c r="D50">
-        <v>21.597899999999996</v>
+        <v>787.51629999999716</v>
       </c>
       <c r="E50">
-        <v>55.56</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>13</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2">
-        <v>1392.0101880000016</v>
-      </c>
-      <c r="D51">
-        <v>310.02700000000038</v>
-      </c>
-      <c r="E51">
-        <v>44.9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>20</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2">
-        <v>1188.0089909999988</v>
-      </c>
-      <c r="D52">
-        <v>206.53430000000034</v>
-      </c>
-      <c r="E52">
-        <v>57.52</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>14</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2">
-        <v>4764.0377489999946</v>
-      </c>
-      <c r="D53">
-        <v>526.02520000000095</v>
-      </c>
-      <c r="E53">
-        <v>90.57</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2">
-        <v>971.95499300000051</v>
-      </c>
-      <c r="D54">
-        <v>145.49510000000009</v>
-      </c>
-      <c r="E54">
-        <v>66.8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>16</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2">
-        <v>1727.9443350000038</v>
-      </c>
-      <c r="D55">
-        <v>374.46700000000044</v>
-      </c>
-      <c r="E55">
-        <v>46.14</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>17</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2">
-        <v>2801.9819490000018</v>
-      </c>
-      <c r="D56">
-        <v>427.40630000000021</v>
-      </c>
-      <c r="E56">
-        <v>65.56</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>18</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2">
-        <v>869.96048499999927</v>
-      </c>
-      <c r="D57">
-        <v>218.12870000000026</v>
-      </c>
-      <c r="E57">
-        <v>39.880000000000003</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>19</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="2">
-        <v>10386.047237999997</v>
-      </c>
-      <c r="D58">
-        <v>787.51629999999716</v>
-      </c>
-      <c r="E58">
         <v>131.88</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D58" xr:uid="{257B41CB-BC06-4035-86EB-862B7C7904CF}"/>
+  <autoFilter ref="A1:D50" xr:uid="{257B41CB-BC06-4035-86EB-862B7C7904CF}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/TablaMorbilidad_Subsectores.xlsx
+++ b/data/TablaMorbilidad_Subsectores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Downloads\TABLERO_STREAMLIT_DASHBOARD\DASHBOARD_Morbilidad_DESPLIEGUE_2\BACKUP DE PAGINAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4A0DA3-F656-4483-9D9E-F478FB2F094D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3557CDD-FD3F-4E29-9F32-A615DEA67E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{3F5E094F-8F70-430D-B0BA-DB553EE45739}"/>
   </bookViews>

--- a/data/TablaMorbilidad_Subsectores.xlsx
+++ b/data/TablaMorbilidad_Subsectores.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Downloads\TABLERO_STREAMLIT_DASHBOARD\DASHBOARD_Morbilidad_DESPLIEGUE_2\BACKUP DE PAGINAS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Downloads\TABLERO_STREAMLIT_DASHBOARD\DASHBOARD_Morbilidad_DESPLIEGUE_2\BACKUP DE PAGINAS\ObservatSaludMental-main - Para GIT UNILLANOS\ObservatSaludMental-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3557CDD-FD3F-4E29-9F32-A615DEA67E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E4F7FC0-89DB-4D5C-B62C-D38C5E152095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{3F5E094F-8F70-430D-B0BA-DB553EE45739}"/>
   </bookViews>
@@ -95,7 +95,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -279,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -311,14 +311,9 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -735,14 +730,14 @@
         <v>5</v>
       </c>
       <c r="C7" s="18">
-        <v>506</v>
+        <v>2340</v>
       </c>
       <c r="D7" s="12">
         <v>3.13</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="21">
         <f>C7/D7</f>
-        <v>161.66134185303514</v>
+        <v>747.60383386581475</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -753,14 +748,14 @@
         <v>5</v>
       </c>
       <c r="C8" s="19">
-        <v>655</v>
+        <v>3334</v>
       </c>
       <c r="D8">
         <v>3.13</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="22">
         <f t="shared" ref="E8:E46" si="0">C8/D8</f>
-        <v>209.26517571884986</v>
+        <v>1065.1757188498402</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -771,14 +766,14 @@
         <v>5</v>
       </c>
       <c r="C9" s="19">
-        <v>441</v>
+        <v>1724</v>
       </c>
       <c r="D9">
         <v>3.13</v>
       </c>
-      <c r="E9" s="25">
-        <f t="shared" si="0"/>
-        <v>140.89456869009584</v>
+      <c r="E9" s="22">
+        <f t="shared" si="0"/>
+        <v>550.79872204472849</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -789,14 +784,14 @@
         <v>5</v>
       </c>
       <c r="C10" s="19">
-        <v>423</v>
+        <v>1702</v>
       </c>
       <c r="D10">
         <v>3.13</v>
       </c>
-      <c r="E10" s="25">
-        <f t="shared" si="0"/>
-        <v>135.14376996805112</v>
+      <c r="E10" s="22">
+        <f t="shared" si="0"/>
+        <v>543.76996805111821</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -807,14 +802,14 @@
         <v>5</v>
       </c>
       <c r="C11" s="19">
-        <v>2214</v>
+        <v>8432</v>
       </c>
       <c r="D11">
         <v>3.13</v>
       </c>
-      <c r="E11" s="25">
-        <f t="shared" si="0"/>
-        <v>707.34824281150168</v>
+      <c r="E11" s="22">
+        <f t="shared" si="0"/>
+        <v>2693.9297124600639</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -825,14 +820,14 @@
         <v>5</v>
       </c>
       <c r="C12" s="19">
-        <v>2074</v>
+        <v>6737</v>
       </c>
       <c r="D12">
         <v>3.13</v>
       </c>
-      <c r="E12" s="25">
-        <f t="shared" si="0"/>
-        <v>662.61980830670927</v>
+      <c r="E12" s="22">
+        <f t="shared" si="0"/>
+        <v>2152.3961661341855</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -843,14 +838,14 @@
         <v>5</v>
       </c>
       <c r="C13" s="19">
-        <v>4035</v>
+        <v>11310</v>
       </c>
       <c r="D13">
         <v>3.13</v>
       </c>
-      <c r="E13" s="25">
-        <f t="shared" si="0"/>
-        <v>1289.1373801916934</v>
+      <c r="E13" s="22">
+        <f t="shared" si="0"/>
+        <v>3613.4185303514378</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -861,14 +856,14 @@
         <v>5</v>
       </c>
       <c r="C14" s="19">
-        <v>2215</v>
+        <v>4556</v>
       </c>
       <c r="D14">
         <v>3.13</v>
       </c>
-      <c r="E14" s="25">
-        <f t="shared" si="0"/>
-        <v>707.66773162939296</v>
+      <c r="E14" s="22">
+        <f t="shared" si="0"/>
+        <v>1455.591054313099</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -879,14 +874,14 @@
         <v>5</v>
       </c>
       <c r="C15" s="19">
-        <v>1001</v>
+        <v>2025</v>
       </c>
       <c r="D15">
         <v>3.13</v>
       </c>
-      <c r="E15" s="25">
-        <f t="shared" si="0"/>
-        <v>319.8083067092652</v>
+      <c r="E15" s="22">
+        <f t="shared" si="0"/>
+        <v>646.96485623003196</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -897,14 +892,14 @@
         <v>5</v>
       </c>
       <c r="C16" s="20">
-        <v>387</v>
+        <v>692</v>
       </c>
       <c r="D16" s="17">
         <v>3.13</v>
       </c>
-      <c r="E16" s="26">
-        <f t="shared" si="0"/>
-        <v>123.64217252396166</v>
+      <c r="E16" s="23">
+        <f t="shared" si="0"/>
+        <v>221.08626198083067</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -915,14 +910,14 @@
         <v>6</v>
       </c>
       <c r="C17" s="18">
-        <v>229</v>
+        <v>1765</v>
       </c>
       <c r="D17" s="12">
         <v>4.5999999999999996</v>
       </c>
-      <c r="E17" s="24">
-        <f t="shared" si="0"/>
-        <v>49.782608695652179</v>
+      <c r="E17" s="21">
+        <f t="shared" si="0"/>
+        <v>383.69565217391306</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -933,14 +928,14 @@
         <v>6</v>
       </c>
       <c r="C18" s="19">
-        <v>269</v>
+        <v>4044</v>
       </c>
       <c r="D18">
         <v>4.5999999999999996</v>
       </c>
-      <c r="E18" s="25">
-        <f t="shared" si="0"/>
-        <v>58.478260869565219</v>
+      <c r="E18" s="22">
+        <f t="shared" si="0"/>
+        <v>879.13043478260875</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -951,14 +946,14 @@
         <v>6</v>
       </c>
       <c r="C19" s="19">
-        <v>291</v>
+        <v>4552</v>
       </c>
       <c r="D19">
         <v>4.5999999999999996</v>
       </c>
-      <c r="E19" s="25">
-        <f t="shared" si="0"/>
-        <v>63.260869565217398</v>
+      <c r="E19" s="22">
+        <f t="shared" si="0"/>
+        <v>989.56521739130437</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -969,14 +964,14 @@
         <v>6</v>
       </c>
       <c r="C20" s="19">
-        <v>258</v>
+        <v>2327</v>
       </c>
       <c r="D20">
         <v>4.5999999999999996</v>
       </c>
-      <c r="E20" s="25">
-        <f t="shared" si="0"/>
-        <v>56.086956521739133</v>
+      <c r="E20" s="22">
+        <f t="shared" si="0"/>
+        <v>505.86956521739137</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -987,14 +982,14 @@
         <v>6</v>
       </c>
       <c r="C21" s="19">
-        <v>1289</v>
+        <v>17803</v>
       </c>
       <c r="D21">
         <v>4.5999999999999996</v>
       </c>
-      <c r="E21" s="25">
-        <f t="shared" si="0"/>
-        <v>280.21739130434787</v>
+      <c r="E21" s="22">
+        <f t="shared" si="0"/>
+        <v>3870.217391304348</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1005,14 +1000,14 @@
         <v>6</v>
       </c>
       <c r="C22" s="19">
-        <v>1308</v>
+        <v>12871</v>
       </c>
       <c r="D22">
         <v>4.5999999999999996</v>
       </c>
-      <c r="E22" s="25">
-        <f t="shared" si="0"/>
-        <v>284.34782608695656</v>
+      <c r="E22" s="22">
+        <f t="shared" si="0"/>
+        <v>2798.04347826087</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1023,14 +1018,14 @@
         <v>6</v>
       </c>
       <c r="C23" s="19">
-        <v>3554</v>
+        <v>18638</v>
       </c>
       <c r="D23">
         <v>4.5999999999999996</v>
       </c>
-      <c r="E23" s="25">
-        <f t="shared" si="0"/>
-        <v>772.60869565217399</v>
+      <c r="E23" s="22">
+        <f t="shared" si="0"/>
+        <v>4051.739130434783</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1041,14 +1036,14 @@
         <v>6</v>
       </c>
       <c r="C24" s="19">
-        <v>1083</v>
+        <v>8656</v>
       </c>
       <c r="D24">
         <v>4.5999999999999996</v>
       </c>
-      <c r="E24" s="25">
-        <f t="shared" si="0"/>
-        <v>235.43478260869568</v>
+      <c r="E24" s="22">
+        <f t="shared" si="0"/>
+        <v>1881.7391304347827</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1059,14 +1054,14 @@
         <v>6</v>
       </c>
       <c r="C25" s="19">
-        <v>432</v>
+        <v>3342</v>
       </c>
       <c r="D25">
         <v>4.5999999999999996</v>
       </c>
-      <c r="E25" s="25">
-        <f t="shared" si="0"/>
-        <v>93.913043478260875</v>
+      <c r="E25" s="22">
+        <f t="shared" si="0"/>
+        <v>726.52173913043487</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1077,14 +1072,14 @@
         <v>6</v>
       </c>
       <c r="C26" s="20">
-        <v>127</v>
+        <v>795</v>
       </c>
       <c r="D26" s="17">
         <v>4.5999999999999996</v>
       </c>
-      <c r="E26" s="26">
-        <f t="shared" si="0"/>
-        <v>27.608695652173914</v>
+      <c r="E26" s="23">
+        <f t="shared" si="0"/>
+        <v>172.82608695652175</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1095,14 +1090,14 @@
         <v>8</v>
       </c>
       <c r="C27" s="18">
-        <v>1677</v>
+        <v>8075</v>
       </c>
       <c r="D27" s="12">
         <v>11.3</v>
       </c>
-      <c r="E27" s="24">
-        <f t="shared" si="0"/>
-        <v>148.40707964601768</v>
+      <c r="E27" s="21">
+        <f t="shared" si="0"/>
+        <v>714.60176991150433</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1113,14 +1108,14 @@
         <v>8</v>
       </c>
       <c r="C28" s="19">
-        <v>2894</v>
+        <v>13800</v>
       </c>
       <c r="D28">
         <v>11.3</v>
       </c>
-      <c r="E28" s="25">
-        <f t="shared" si="0"/>
-        <v>256.10619469026545</v>
+      <c r="E28" s="22">
+        <f t="shared" si="0"/>
+        <v>1221.2389380530972</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1131,14 +1126,14 @@
         <v>8</v>
       </c>
       <c r="C29" s="19">
-        <v>2226</v>
+        <v>12124</v>
       </c>
       <c r="D29">
         <v>11.3</v>
       </c>
-      <c r="E29" s="25">
-        <f t="shared" si="0"/>
-        <v>196.99115044247787</v>
+      <c r="E29" s="22">
+        <f t="shared" si="0"/>
+        <v>1072.9203539823009</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1149,14 +1144,14 @@
         <v>8</v>
       </c>
       <c r="C30" s="19">
-        <v>1451</v>
+        <v>6876</v>
       </c>
       <c r="D30">
         <v>11.3</v>
       </c>
-      <c r="E30" s="25">
-        <f t="shared" si="0"/>
-        <v>128.40707964601768</v>
+      <c r="E30" s="22">
+        <f t="shared" si="0"/>
+        <v>608.49557522123894</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1167,14 +1162,14 @@
         <v>8</v>
       </c>
       <c r="C31" s="19">
-        <v>6247</v>
+        <v>37429</v>
       </c>
       <c r="D31">
         <v>11.3</v>
       </c>
-      <c r="E31" s="25">
-        <f t="shared" si="0"/>
-        <v>552.83185840707961</v>
+      <c r="E31" s="22">
+        <f t="shared" si="0"/>
+        <v>3312.3008849557518</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1185,14 +1180,14 @@
         <v>8</v>
       </c>
       <c r="C32" s="19">
-        <v>5582</v>
+        <v>24874</v>
       </c>
       <c r="D32">
         <v>11.3</v>
       </c>
-      <c r="E32" s="25">
-        <f t="shared" si="0"/>
-        <v>493.98230088495575</v>
+      <c r="E32" s="22">
+        <f t="shared" si="0"/>
+        <v>2201.2389380530972</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1203,14 +1198,14 @@
         <v>8</v>
       </c>
       <c r="C33" s="19">
-        <v>14344</v>
+        <v>52642</v>
       </c>
       <c r="D33">
         <v>11.3</v>
       </c>
-      <c r="E33" s="25">
-        <f t="shared" si="0"/>
-        <v>1269.3805309734512</v>
+      <c r="E33" s="22">
+        <f t="shared" si="0"/>
+        <v>4658.5840707964599</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1221,14 +1216,14 @@
         <v>8</v>
       </c>
       <c r="C34" s="19">
-        <v>4390</v>
+        <v>18754</v>
       </c>
       <c r="D34">
         <v>11.3</v>
       </c>
-      <c r="E34" s="25">
-        <f t="shared" si="0"/>
-        <v>388.49557522123894</v>
+      <c r="E34" s="22">
+        <f t="shared" si="0"/>
+        <v>1659.646017699115</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1239,14 +1234,14 @@
         <v>8</v>
       </c>
       <c r="C35" s="19">
-        <v>3837</v>
+        <v>11654</v>
       </c>
       <c r="D35">
         <v>11.3</v>
       </c>
-      <c r="E35" s="25">
-        <f t="shared" si="0"/>
-        <v>339.55752212389376</v>
+      <c r="E35" s="22">
+        <f t="shared" si="0"/>
+        <v>1031.3274336283184</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1257,14 +1252,14 @@
         <v>8</v>
       </c>
       <c r="C36" s="19">
-        <v>902</v>
+        <v>2861</v>
       </c>
       <c r="D36">
         <v>11.3</v>
       </c>
-      <c r="E36" s="25">
-        <f t="shared" si="0"/>
-        <v>79.82300884955751</v>
+      <c r="E36" s="22">
+        <f t="shared" si="0"/>
+        <v>253.18584070796459</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1275,158 +1270,158 @@
         <v>7</v>
       </c>
       <c r="C37" s="18">
-        <v>34</v>
+        <v>166</v>
       </c>
       <c r="D37" s="12">
         <v>1.23</v>
       </c>
-      <c r="E37" s="24">
-        <f t="shared" si="0"/>
-        <v>27.64227642276423</v>
+      <c r="E37" s="21">
+        <f t="shared" si="0"/>
+        <v>134.95934959349594</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="22">
-        <v>59</v>
-      </c>
-      <c r="D38" s="23">
+      <c r="C38" s="19">
+        <v>345</v>
+      </c>
+      <c r="D38">
         <v>1.23</v>
       </c>
-      <c r="E38" s="25">
-        <f t="shared" si="0"/>
-        <v>47.967479674796749</v>
+      <c r="E38" s="22">
+        <f t="shared" si="0"/>
+        <v>280.48780487804879</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="22">
-        <v>52</v>
-      </c>
-      <c r="D39" s="23">
+      <c r="C39" s="19">
+        <v>214</v>
+      </c>
+      <c r="D39">
         <v>1.23</v>
       </c>
-      <c r="E39" s="25">
-        <f t="shared" si="0"/>
-        <v>42.27642276422764</v>
+      <c r="E39" s="22">
+        <f t="shared" si="0"/>
+        <v>173.98373983739839</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C40" s="22">
-        <v>33</v>
-      </c>
-      <c r="D40" s="23">
+      <c r="C40" s="19">
+        <v>198</v>
+      </c>
+      <c r="D40">
         <v>1.23</v>
       </c>
-      <c r="E40" s="25">
-        <f t="shared" si="0"/>
-        <v>26.829268292682926</v>
+      <c r="E40" s="22">
+        <f t="shared" si="0"/>
+        <v>160.97560975609755</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B41" s="21" t="s">
+      <c r="B41" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C41" s="22">
-        <v>130</v>
-      </c>
-      <c r="D41" s="23">
+      <c r="C41" s="19">
+        <v>755</v>
+      </c>
+      <c r="D41">
         <v>1.23</v>
       </c>
-      <c r="E41" s="25">
-        <f t="shared" si="0"/>
-        <v>105.6910569105691</v>
+      <c r="E41" s="22">
+        <f t="shared" si="0"/>
+        <v>613.82113821138216</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B42" s="21" t="s">
+      <c r="B42" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="22">
-        <v>51</v>
-      </c>
-      <c r="D42" s="23">
+      <c r="C42" s="19">
+        <v>308</v>
+      </c>
+      <c r="D42">
         <v>1.23</v>
       </c>
-      <c r="E42" s="25">
-        <f t="shared" si="0"/>
-        <v>41.463414634146339</v>
+      <c r="E42" s="22">
+        <f t="shared" si="0"/>
+        <v>250.40650406504065</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B43" s="21" t="s">
+      <c r="B43" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="22">
-        <v>431</v>
-      </c>
-      <c r="D43" s="23">
+      <c r="C43" s="19">
+        <v>1427</v>
+      </c>
+      <c r="D43">
         <v>1.23</v>
       </c>
-      <c r="E43" s="25">
-        <f t="shared" si="0"/>
-        <v>350.40650406504068</v>
+      <c r="E43" s="22">
+        <f t="shared" si="0"/>
+        <v>1160.1626016260163</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B44" s="21" t="s">
+      <c r="B44" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="22">
-        <v>49</v>
-      </c>
-      <c r="D44" s="23">
+      <c r="C44" s="19">
+        <v>450</v>
+      </c>
+      <c r="D44">
         <v>1.23</v>
       </c>
-      <c r="E44" s="25">
-        <f t="shared" si="0"/>
-        <v>39.837398373983739</v>
+      <c r="E44" s="22">
+        <f t="shared" si="0"/>
+        <v>365.85365853658539</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B45" s="21" t="s">
+      <c r="B45" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="22">
-        <v>44</v>
-      </c>
-      <c r="D45" s="23">
+      <c r="C45" s="19">
+        <v>127</v>
+      </c>
+      <c r="D45">
         <v>1.23</v>
       </c>
-      <c r="E45" s="25">
-        <f t="shared" si="0"/>
-        <v>35.772357723577237</v>
+      <c r="E45" s="22">
+        <f t="shared" si="0"/>
+        <v>103.2520325203252</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -1437,14 +1432,14 @@
         <v>7</v>
       </c>
       <c r="C46" s="20">
-        <v>13</v>
+        <v>155</v>
       </c>
       <c r="D46" s="17">
         <v>1.23</v>
       </c>
-      <c r="E46" s="26">
-        <f t="shared" si="0"/>
-        <v>10.56910569105691</v>
+      <c r="E46" s="23">
+        <f t="shared" si="0"/>
+        <v>126.01626016260163</v>
       </c>
     </row>
   </sheetData>
